--- a/Tableau_to_SiS_Task_Assignment.xlsx
+++ b/Tableau_to_SiS_Task_Assignment.xlsx
@@ -127,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -159,9 +159,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -181,14 +178,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1092,19 +1089,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>3 - NEEDS YOUR ACCOUNT</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>YES - Snowflake</t>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>1 - INDEPENDENT</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>No - has Snowflake</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Needs the Streamlit-in-Snowflake sandbox to verify the blank-map behavior and prove the fallback. Cannot be reproduced locally - the blank map IS a sandbox-only platform limit.</t>
+          <t>Needs the Streamlit-in-Snowflake sandbox to verify the blank-map behavior and prove the fallback (cannot be reproduced locally - the blank map IS a sandbox-only platform limit). CONFIRMED 2026-08-13: the resource has Snowflake/Snowsight access, so this is theirs to do. Needs the connections.toml entry for wb19670-c2gpartners.</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1148,12 +1145,12 @@
           <t>D3</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>2 - ONE-TIME UNBLOCK</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Decision D3</t>
         </is>
@@ -1241,36 +1238,36 @@
       <c r="L14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="13" t="n"/>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="A15" s="12" t="n"/>
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>TOTAL (estimated days)</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="15">
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="14">
         <f>SUM(D5:D14)</f>
         <v/>
       </c>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="16">
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="15">
         <f>SUMIF(F5:F14,"1 - INDEPENDENT",D5:D14)</f>
         <v/>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>days independent</t>
         </is>
       </c>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="13" t="n"/>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>All 10 items estimated from MVP_ACCELERATOR_SCOPE.md's own tracked figures.</t>
         </is>
       </c>
-      <c r="K15" s="13" t="n"/>
-      <c r="L15" s="13" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1314,7 +1311,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Start on B2 (needs no decision). B1 and B6 unblock when decisions D1/D2 land. Primary files: validation_report.py, validation_adapter.py, deep_validation.py, app_screenshot.py. Full context: HANDOFF_TRACK_B_VALIDATION.md</t>
+          <t>UPDATED 2026-08-13: D1/D2 decided, so B1/B2/B6/B7/B8 are ALL unblocked - start on any of them. Only B3/B4 still wait on the E1/E2 crosstab exports, and B5 needs Snowflake. Primary files: validation_report.py, validation_adapter.py, deep_validation.py, app_screenshot.py. Full context (incl. the D1/D2 rationale): HANDOFF_TRACK_B_VALIDATION.md</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1385,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>order_match chart-level FAIL semantics (validation_report.py:198, made a structural_failure at line 206). Live on Regional Analysis, TWO fully-evidenced charts read chart-level FAIL while EVERY individual cell passes - purely from row sequence. Meaningful for a ranked list; not for a grouped bar chart.</t>
+          <t>order_match chart-level FAIL semantics (validation_report.py:198, made a structural_failure at line 206). Live on Regional Analysis, TWO fully-evidenced charts read chart-level FAIL while EVERY individual cell passes - purely from row sequence. DECIDED: implement as a structural FAIL only for ranked/top-N charts; informational flag everywhere else.</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -1403,22 +1400,22 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>2 - ONE-TIME UNBLOCK</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>Decision D1</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>1 - INDEPENDENT</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>No - D1 DECIDED</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Work is fully offline (validation_report.py + local fixtures). Only your D1 ruling is missing - about 2 minutes.</t>
+          <t>UNBLOCKED 2026-08-13. Sharath's ruling: order is a structural FAIL only for ranked/top-N charts; informational elsewhere. Work is fully offline (validation_report.py + local fixtures). Full rationale in HANDOFF_TRACK_B_VALIDATION.md item 1.</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1428,17 +1425,17 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Gate proves BOTH sides: a ranked list STILL fails on wrong order, a grouped bar chart no longer does. DO NOT simply delete the check - it touches the vendored engine's structural-failure semantics.</t>
-        </is>
-      </c>
-      <c r="K5" s="19" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Gate proves BOTH sides: a ranked list STILL fails on wrong order, a grouped bar chart no longer does. DO NOT simply delete the check, and do NOT weaken it for ranked lists - it touches the vendored engine's structural-failure semantics.</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>Ready</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>Needs decision D1</t>
+          <t>D1 decided 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1527,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>2 - ONE-TIME UNBLOCK</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>ONE sample CSV</t>
         </is>
@@ -1588,12 +1585,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>2 - ONE-TIME UNBLOCK</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>ONE sample CSV</t>
         </is>
@@ -1646,19 +1643,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>3 - NEEDS YOUR ACCOUNT</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>YES - Snowflake</t>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>1 - INDEPENDENT</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>No - has Snowflake</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Needs the real backend table to diagnose which of three causes applies (calc gap / column-mapping gap / column genuinely absent). Cannot be determined from the workbook XML alone.</t>
+          <t>Needs the real backend table to diagnose which of three causes applies (calc gap / column-mapping gap / column genuinely absent) - cannot be determined from the workbook XML alone. CONFIRMED 2026-08-13: the resource has Snowflake/Snowsight access, so this is theirs. Needs the connections.toml entry for wb19670-c2gpartners.</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1701,42 +1698,42 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>2 - ONE-TIME UNBLOCK</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>Decision D2</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>1 - INDEPENDENT</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>No - D2 DECIDED</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>The comparison numbers are ALREADY proven live (Tableau 0.2/0.8/0.4 vs app 0.1/0.2/0.1). The one-line fix is local. Only your D2 ruling is missing. Deploying it later needs Snowflake.</t>
+          <t>UNBLOCKED 2026-08-13. Sharath's ruling: respect the workbook's declared aggregation - a curated profile entry applies only where the workbook declares that same agg. Comparison numbers already proven live. Fix is local; DEPLOYING it later needs Snowflake, and it changes numbers the deployed app renders. See HANDOFF_TRACK_B_VALIDATION.md item 5b.</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>profile_superstore.py</t>
+          <t>profile_superstore.py, engine.py (resolve_measure ~line 218-255)</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Numbers match Tableau's REST-confirmed values WITHOUT breaking the other sheets where AVG is legitimately correct. Unfixed to date precisely because of that tension - it changes numbers the DEPLOYED app renders.</t>
-        </is>
-      </c>
-      <c r="K10" s="19" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>DECIDED: respect the workbook's declared aggregation - a curated profile entry applies ONLY where the workbook declares that same agg, otherwise the workbook wins. This is the STRUCTURAL fix (kills the whole bug class), not a one-line swap to SUM. Done when Product Detail Sheet Discount matches Tableau's 0.2/0.8/0.4 AND sheets where AVG is correct still read AVG, gated both ways. Changes numbers the DEPLOYED app renders -&gt; needs redeploy + tracker update.</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>Ready</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>Needs decision D2</t>
+          <t>D2 decided 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1861,30 +1858,30 @@
       <c r="L12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="13" t="n"/>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="A13" s="12" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>TOTAL - deliberately NOT estimated</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="13" t="n"/>
-      <c r="H13" s="13" t="n"/>
-      <c r="I13" s="13" t="n"/>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>DELIBERATELY NOT ESTIMATED: B2-B5 are investigate-then-fix, and no honest day figure exists yet. Resource 2's day-one deliverable is a real estimate for B2-B5, reported back before committing to a timeline.</t>
         </is>
       </c>
-      <c r="K13" s="13" t="n"/>
-      <c r="L13" s="13" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1901,27 +1898,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DECISIONS REQUIRED BEFORE DAY ONE</t>
+          <t>DECISIONS - D1 and D2 DECIDED 2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>These block real tickets. None is an engineering call - each changes numbers or verdicts the client sees.</t>
+          <t>D1 and D2 are answered, which unblocked B1 and B6. Only the two crosstab exports (E1/E2) remain outstanding from Sharath. D3 is not blocking anyone.</t>
         </is>
       </c>
     </row>
@@ -1933,110 +1930,110 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Decision needed from Sharath</t>
+          <t>The question</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Recommendation / options</t>
+          <t>SHARATH'S RULING</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Why it can't be delegated</t>
+          <t>Status / notes</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Blocks</t>
+          <t>Task</t>
         </is>
       </c>
     </row>
     <row r="5" ht="76" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>order_match: should an exact row-ORDER mismatch fail a chart that is NOT a ranked list? Today it does - so on Regional Analysis two charts read chart-level FAIL while every single cell passes.</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>RECOMMENDED: order is semantic only for ranked / top-N charts; elsewhere demote it to an informational flag.</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>Changes the vendored comparison engine's strictness - i.e. changes what 'validated' means in a client deliverable.</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>B1</t>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>DECIDED 2026-08-13: order is a structural FAIL ONLY for charts where display order carries meaning (rank tables, top-N). Everywhere else it becomes an INFORMATIONAL flag. Do not delete the check; do not weaken it for ranked lists. The gate must prove BOTH directions.</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>DECIDED - B1 is unblocked and ready to build. Rationale is written into HANDOFF_TRACK_B_VALIDATION.md item 1.</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>B1 - READY</t>
         </is>
       </c>
     </row>
     <row r="6" ht="76" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>Discount = AVG or SUM? profile_superstore.py:20 curates AVG(DISCOUNT), overriding the workbook's declared agg=sum. Tableau's own REST values prove the app is wrong (app 0.1/0.2/0.1 vs Tableau 0.2/0.8/0.4).</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>Needs your call: fix to honour the workbook's declared agg, or keep the curated AVG and scope where it applies. AVG is legitimately correct on OTHER sheets.</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>The fix changes numbers the DEPLOYED app renders in front of a client.</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>B6</t>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Discount = AVG or SUM? profile_superstore.py:20 curates AVG(DISCOUNT), overriding the workbook's declared agg=sum. Tableau's own REST values prove the app is wrong (app 0.1/0.2/0.1 vs Tableau 0.2/0.8/0.4; backend agrees with Tableau).</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>DECIDED 2026-08-13: respect the WORKBOOK's declared aggregation. A curated profile entry applies only where the workbook declares that same agg; otherwise the workbook wins. Structural fix, NOT a one-line swap to SUM - it closes the whole bug class rather than this one measure.</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>DECIDED - B6 is unblocked. NOTE: this changes numbers the DEPLOYED app renders, so it needs a redeploy + tracker update. See HANDOFF_TRACK_B_VALIDATION.md item 5b.</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>B6 - READY</t>
         </is>
       </c>
     </row>
     <row r="7" ht="76" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Is the Track A backlog order still the priority you want? The list follows MVP_ACCELERATOR_SCOPE.md. Rich tooltips (A9) is recorded as 'user deprioritized'.</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>Confirm A9 stays last, and that bins -&gt; histogram is the right P0 opener.</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>Sequencing / business call, not an engineering one.</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>NOT formally answered - the MVP_ACCELERATOR_SCOPE.md order stands by default and A9 remains last. Confirm before anyone spends a day on A9.</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Resource 1 is NOT blocked by this: A1 (Bins) was never gated on it.</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>A-track order</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>NOT ASSIGNED TO EITHER RESOURCE - needs Snowsight access, not an engineer</t>
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>STILL OUTSTANDING FROM SHARATH - two file exports (~15 min), unblocks B3 + B4</t>
         </is>
       </c>
     </row>
@@ -2048,238 +2045,327 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>Export needed</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Why it's blocking</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Unblocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="66" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>One Tableau crosstab CSV in the PIVOTED / LONG shape (Measure Names / Measure Values columns).</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>CONFIRMED MISSING: no live Tableau crosstab CSV is saved anywhere in the repo, and there is no fixture for the pivoted shape at all (checked tests/fixtures/ and every reports/ pack). B3 cannot be worked offline without it.</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Worksheet -&gt; Export -&gt; Data (or Download -&gt; Crosstab -&gt; CSV in Tableau Cloud/Server). Save into tests/fixtures/ and commit.</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>One Tableau crosstab CSV whose header carries a DATE-PART grouping (e.g. 'Month of Order Date').</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Same situation as E1 - none saved locally. B4 needs a real header to align against, not an assumed format.</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Same export path. Save into tests/fixtures/ and commit - both then become PERMANENT regression fixtures, not just a one-time unblock.</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>NOT ASSIGNED TO EITHER RESOURCE - needs Snowsight access, not an engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Est</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Suggested owner</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="18" ht="62" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>R9 UI upload confirmation - upload Workbooks/R9_Live_Join_Orders_Product_Category.twb through the deployed pipeline_demo app. Code-complete, gated, already verified against the real account via pipeline.onboard(). Same final UI confirmation R3 and R10 passed.</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>~10 min, no dev work</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>DELEGATE to Resource 2 (they have Snowsight)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Closes the last open data-model verification item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="62" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>MVP sign-off (item #6) - your own visual confirmation in Snowsight. The last open MVP item; explicitly not dev work.</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Sharath</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>MVP reads 5 of 6 done; this is the 6th.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="62" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Confirm R8 deploy status - the Cortex-vision re-wire was marked 'NOT YET DEPLOYED' on 2026-08-07, and ARCHITECTURE.md:1579 notes one such banner is itself stale. Needs a look at what is actually live.</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>~15 min</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Whoever has Snowsight access</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Closes the last open data-model verification item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="62" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>MVP sign-off (item #6) - your own visual confirmation in Snowsight. The last open MVP item; explicitly not dev work.</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Sharath</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>MVP reads 5 of 6 done; this is the 6th.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="62" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Confirm R8 deploy status - the Cortex-vision re-wire was marked 'NOT YET DEPLOYED' on 2026-08-07, and ARCHITECTURE.md:1579 notes one such banner is itself stale. Needs a look at what is actually live.</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>~15 min</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Whoever has Snowsight access</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Do this before anyone trusts either claim in the docs.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>DEPENDENCY TIER LEGEND (the 'Dependency tier' column on both resource tabs)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="62" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
+    <row r="24" ht="62" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>1 - INDEPENDENT</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>Fully self-contained. Everything needed is already in the repo - the corpus workbooks live in Workbooks/, the parsed IR fixtures are committed, and the regression suite runs entirely offline on DuckDB + fake Snowflake sessions (verified 2026-08-13 by a full 81-gate run with NO credentials). Hand over the repo and the resource is productive immediately.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="62" customHeight="1">
-      <c r="A19" s="25" t="inlineStr">
+    <row r="25" ht="62" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>2 - ONE-TIME UNBLOCK</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>Needs ONE thing from you, once - then fully offline. Either a 2-minute decision (D1/D2/D3) or a single exported sample file. Total cost to you across all five tier-2 tasks is roughly 30 minutes, and it is the highest-leverage time you can spend on this handoff.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="62" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
-        <is>
-          <t>3 - NEEDS YOUR ACCOUNT</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
+    <row r="26" ht="62" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>3 - NEEDS SNOWFLAKE</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>Genuinely needs your Snowflake / Snowsight account and cannot be delegated without credentials. NOTE: this is about DIAGNOSIS. Deploying any finished fix also needs Snowflake, but that batches - both resources build and gate-lock offline, and you deploy in a single pass.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
-        <is>
-          <t>SUMMARY: 11 of 18 tasks are tier 1 (zero dependency on you). Resource 1 has 10.5 of its 12.5 days fully independent - only A8 needs your account. Resource 2 is the one that needs you: only B2/B7/B8 are immediately independent, but making decisions D1+D2 and exporting two sample crosstabs converts four more tasks to fully independent, leaving only B5 account-bound.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>SUMMARY (updated 2026-08-13, after D1/D2 were decided AND both resources were confirmed to have Snowflake/Snowsight access): 16 of 18 tasks are now tier 1 - zero dependency on Sharath. Resource 1: ALL 10 tasks independent (A8 included, since it only needed the Snowflake sandbox). Resource 2: B1/B2/B5/B6/B7/B8 all independent. ONLY B3 and B4 remain gated, on the E1/E2 crosstab exports - and even those become self-serve if Resource 2 is given Tableau access, since they could export the two crosstabs themselves. S1/S3 should now be DELEGATED, not kept by Sharath. BOTH RESOURCES CAN START IMMEDIATELY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>GROUND RULES - BOTH RESOURCES</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>- COLLISION RISK: both tracks can touch engine.py. Track A owns it for new chart renderers. Track B may need it for channel captions (engine.py does not set real Tableau captions as axis/tooltip titles - documented as the 'biggest lever' for validation; the 2026-08-11 pie-theta fix was exactly this). RULE: Track B does not edit engine.py without telling Track A first. A caption change also alters the shipped app's visuals, so it needs its own decision.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>- NO VERSION CONTROL in this working directory. With two people editing, set up git first or partition file ownership manually - there is no branch isolation and no undo.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>- Regression suite must stay green: run 'python tests/test_regression.py' from the repo root. Verified green 2026-08-13: 82 gates defined, 81 auto-run all passing, 1 deliberately manual (needs a live session).</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>- Every fix needs a gate with PROVEN TEETH - revert your fix and confirm the gate goes red.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>- Update status_config.json + MVP_ACCELERATOR_SCOPE.md IN THE SAME CHANGE as the feature/fix, not as a follow-up. test_tracker_consistency enforces part of this.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>- TRUST INVARIANT: BLOCKED (never measured) and FAIL (proven wrong) must never look the same. A missing proof cannot become a pass.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="40" customHeight="1">
-      <c r="A31" s="24" t="inlineStr">
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>- TRUST INVARIANT: never guess. Where the code refuses - an ambiguous crosstab, an unresolvable column, a multi-fact graph - that refusal IS the feature. At least two refusals here exist because a looser version was tried and found genuinely ambiguous against live data.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t>- TRUST INVARIANT: nothing is silently dropped. Every unsupported construct produces a named finding, never a blank chart or a guessed number.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="A30:E30"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
     <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A32:E32"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:E37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
